--- a/artfynd/A 46721-2025 artfynd.xlsx
+++ b/artfynd/A 46721-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131139231</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131138011</v>
       </c>
       <c r="B3" t="n">
-        <v>57064</v>
+        <v>57066</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>131138170</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>131145711</v>
       </c>
       <c r="B5" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 46721-2025 artfynd.xlsx
+++ b/artfynd/A 46721-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131139231</v>
       </c>
       <c r="B2" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131138011</v>
       </c>
       <c r="B3" t="n">
-        <v>57066</v>
+        <v>57067</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>131138170</v>
       </c>
       <c r="B4" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>131145711</v>
       </c>
       <c r="B5" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 46721-2025 artfynd.xlsx
+++ b/artfynd/A 46721-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131139231</v>
       </c>
       <c r="B2" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>131138170</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>131145711</v>
       </c>
       <c r="B5" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 46721-2025 artfynd.xlsx
+++ b/artfynd/A 46721-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131139231</v>
       </c>
       <c r="B2" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131138011</v>
       </c>
       <c r="B3" t="n">
-        <v>57067</v>
+        <v>57070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>131138170</v>
       </c>
       <c r="B4" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>131145711</v>
       </c>
       <c r="B5" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 46721-2025 artfynd.xlsx
+++ b/artfynd/A 46721-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131139231</v>
       </c>
       <c r="B2" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131138011</v>
       </c>
       <c r="B3" t="n">
-        <v>57070</v>
+        <v>57071</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>131138170</v>
       </c>
       <c r="B4" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>131145711</v>
       </c>
       <c r="B5" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 46721-2025 artfynd.xlsx
+++ b/artfynd/A 46721-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131139231</v>
       </c>
       <c r="B2" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131138011</v>
       </c>
       <c r="B3" t="n">
-        <v>57071</v>
+        <v>57077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>131138170</v>
       </c>
       <c r="B4" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>131145711</v>
       </c>
       <c r="B5" t="n">
-        <v>58051</v>
+        <v>58057</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 46721-2025 artfynd.xlsx
+++ b/artfynd/A 46721-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131139231</v>
+        <v>7262643</v>
       </c>
       <c r="B2" t="n">
-        <v>57898</v>
+        <v>79946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Björndalskvarnen, Dlr</t>
+          <t>Pajsoån, Dammfallet, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479597</v>
+        <v>479865</v>
       </c>
       <c r="R2" t="n">
-        <v>6674083</v>
+        <v>6674038</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,22 +742,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2014-04-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2014-04-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,28 +756,44 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>vrak # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131138011</v>
+        <v>131138170</v>
       </c>
       <c r="B3" t="n">
-        <v>57077</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,16 +801,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -823,7 +826,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -872,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131138170</v>
+        <v>131139231</v>
       </c>
       <c r="B4" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,31 +941,21 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dammfallet, Dlr</t>
+          <t>Björndalskvarnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479766</v>
+        <v>479597</v>
       </c>
       <c r="R4" t="n">
-        <v>6674165</v>
+        <v>6674083</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -994,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,35 +1024,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131145711</v>
+        <v>131138011</v>
       </c>
       <c r="B5" t="n">
-        <v>58057</v>
+        <v>57132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1067,17 +1070,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björndalskvarnen, Dlr</t>
+          <t>Dammfallet, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479758</v>
+        <v>479766</v>
       </c>
       <c r="R5" t="n">
-        <v>6674302</v>
+        <v>6674165</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,14 +1107,19 @@
           <t>2026-02-13</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-13</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2 st Medobservatör Sture Lindstrand</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,6 +1143,113 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131145711</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Björndalskvarnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>479758</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6674302</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2 st Medobservatör Sture Lindstrand</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
